--- a/dietitian_forms/020_nutrition_quiz--dietitian_forms.xlsx
+++ b/dietitian_forms/020_nutrition_quiz--dietitian_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'undisclosed'}</t>
+          <t>undisclosed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Undisclosed'}</t>
+          <t>Undisclosed</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'lose_weight'}</t>
+          <t>lose_weight</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Lose weight'}</t>
+          <t>Lose weight</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'manage_blood_sugar'}</t>
+          <t>manage_blood_sugar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Manage blood sugar'}</t>
+          <t>Manage blood sugar</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'improve_gut_health'}</t>
+          <t>improve_gut_health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Improve gut health'}</t>
+          <t>Improve gut health</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'omnivore'}</t>
+          <t>omnivore</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Omnivore'}</t>
+          <t>Omnivore</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'raw_food'}</t>
+          <t>raw_food</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Raw food'}</t>
+          <t>Raw food</t>
         </is>
       </c>
     </row>
